--- a/scraper/salidas/idealista_Segovia_alquiler.xlsx
+++ b/scraper/salidas/idealista_Segovia_alquiler.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ71"/>
+  <dimension ref="A1:AX77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -696,16 +696,6 @@
       <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>Comunidad Autonoma</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>Lat</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>Lon</t>
         </is>
       </c>
     </row>
@@ -858,12 +848,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY2" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1044,12 +1028,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY3" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1210,12 +1188,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY4" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1378,12 +1350,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY5" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1536,12 +1502,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY6" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1708,12 +1668,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY7" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1858,12 +1812,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY8" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2014,12 +1962,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY9" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2170,12 +2112,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY10" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2322,12 +2258,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY11" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2484,12 +2414,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY12" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2652,12 +2576,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY13" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2820,12 +2738,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY14" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2972,12 +2884,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY15" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3154,12 +3060,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY16" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3324,12 +3224,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY17" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3490,12 +3384,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY18" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3650,12 +3538,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY19" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3810,12 +3692,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY20" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3962,12 +3838,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY21" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4126,12 +3996,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY22" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4290,12 +4154,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY23" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4458,12 +4316,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY24" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4626,12 +4478,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY25" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4782,12 +4628,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY26" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4946,12 +4786,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY27" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -5140,12 +4974,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY28" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5312,12 +5140,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY29" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5480,12 +5302,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY30" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5620,12 +5436,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY31" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5788,12 +5598,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY32" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5928,12 +5732,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY33" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6094,12 +5892,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY34" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6248,12 +6040,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY35" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6396,12 +6182,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY36" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6558,12 +6338,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY37" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6720,12 +6494,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY38" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6872,12 +6640,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY39" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -7046,12 +6808,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY40" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -7202,12 +6958,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY41" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ41" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -7350,12 +7100,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY42" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -7516,12 +7260,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY43" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ43" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -7680,12 +7418,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY44" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ44" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -7840,12 +7572,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY45" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ45" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -7998,12 +7724,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY46" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ46" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -8164,12 +7884,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY47" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ47" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -8332,12 +8046,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY48" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ48" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -8498,12 +8206,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY49" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ49" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -8664,12 +8366,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY50" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ50" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -8824,12 +8520,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY51" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ51" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -8990,12 +8680,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY52" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ52" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -9150,12 +8834,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY53" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ53" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -9310,12 +8988,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY54" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ54" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -9488,12 +9160,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY55" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ55" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -9666,12 +9332,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY56" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ56" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -9836,12 +9496,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY57" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ57" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -9994,12 +9648,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY58" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ58" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -10166,12 +9814,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY59" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ59" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -10324,12 +9966,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY60" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ60" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -10494,12 +10130,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY61" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ61" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -10642,12 +10272,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY62" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ62" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -10792,12 +10416,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY63" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ63" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -10962,12 +10580,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY64" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ64" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -11114,12 +10726,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY65" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ65" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -11284,12 +10890,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY66" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ66" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -11432,12 +11032,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY67" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ67" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -11604,12 +11198,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY68" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ68" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -11766,12 +11354,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY69" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ69" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -11934,12 +11516,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY70" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ70" t="n">
-        <v>-3.705</v>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -12104,11 +11680,927 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY71" t="n">
-        <v>40.415</v>
-      </c>
-      <c r="AZ71" t="n">
-        <v>-3.705</v>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Alquiler de piso en Calle de la Muerte y Dia Vida</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>790</v>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>6 horas</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>1053</v>
+      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="n">
+        <v>1</v>
+      </c>
+      <c r="L72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>piso</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>orientación sur</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>4ª</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr"/>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>de la Muerte y Dia Vida</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr"/>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Distrito Centro</t>
+        </is>
+      </c>
+      <c r="AD72" t="inlineStr"/>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="AG72" t="inlineStr"/>
+      <c r="AH72" t="inlineStr"/>
+      <c r="AI72" t="inlineStr"/>
+      <c r="AJ72" t="inlineStr"/>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Segunda mano / buen estado</t>
+        </is>
+      </c>
+      <c r="AL72" t="inlineStr"/>
+      <c r="AM72" t="inlineStr"/>
+      <c r="AN72" t="inlineStr"/>
+      <c r="AO72" t="inlineStr"/>
+      <c r="AP72" t="inlineStr"/>
+      <c r="AQ72" t="inlineStr">
+        <is>
+          <t>Agencia</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>Inmosales</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr">
+        <is>
+          <t>Si estás buscando un estudio en pleno centro de Segovia, recién reformado, contacta con Inmosales y te mostramos todos los detalles: - Dispone de baño recién reformado, con cuidados acabados de sanitarios y griferías. - Amplia zona de cocina a estrenar y perfectamente integrada en la sala principal, que podrás ambientar como zona de descanso o de estudio. - Amplio dormitorio independiente de la zona principal, en la que también podrás recibir a tus invitados Muy luminoso, con orientación sur, que te permitirá reducir el consumo de la calefacción eléctrica con modernos radiadores, y disfrutar de unas vistas estupendas a la plaza de Somorrostro.. . Con todas las ventajas de vivir a 200m del Acueducto, con todas las comodidades (ascensor, portero automático, mobiliario a estrenar,... ) No esperes más y aprovecha esta oportunidad para tener tu apartamento independiente, recien reformado y en pleno centro de Segovia...</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr">
+        <is>
+          <t>17/01/2026</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/104844245/</t>
+        </is>
+      </c>
+      <c r="AV72" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AW72" t="inlineStr"/>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Alquiler de piso en Calle Almira</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>750</v>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>8 horas</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" s="2" t="n">
+        <v>1974</v>
+      </c>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="n">
+        <v>1</v>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>piso</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>orientación sur</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2ª</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr"/>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>Almira</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr"/>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Distrito Centro</t>
+        </is>
+      </c>
+      <c r="AD73" t="inlineStr"/>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="AG73" t="inlineStr"/>
+      <c r="AH73" t="inlineStr"/>
+      <c r="AI73" t="inlineStr"/>
+      <c r="AJ73" t="inlineStr"/>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Segunda mano / buen estado</t>
+        </is>
+      </c>
+      <c r="AL73" t="inlineStr"/>
+      <c r="AM73" t="inlineStr"/>
+      <c r="AN73" t="inlineStr"/>
+      <c r="AO73" t="inlineStr"/>
+      <c r="AP73" t="inlineStr"/>
+      <c r="AQ73" t="inlineStr">
+        <is>
+          <t>Agencia</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>Zazume</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr">
+        <is>
+          <t>Zazume te trae esta cómoda y acogedora vivienda EXTERIOR con 2 BALCONES en Segovia. *Contrato de larga estancia (5 años) de obligado cumplimiento 2 años. No se aceptan mascotas. * En Zazume estaremos permanentemente a tu disposición para que tu hogar sea una experiencia inolvidable. ¡Alquila tu casa y dedícate a vivir! Este inmueble consta de: - 1 dormitorio - 1 cuarto de baño completo - salón - comedor - cocina equipada con electrodomésticos como frigorífico y lavadora - 2 balcones Dispone de un altillo con una habitación adicional arriba con 15m2 adicionales a los 38m2. Los gastos de comunidad son a cargo del propietario y los gastos variables a cargo del inquilino. La vivienda tiene vistas al acueducto, y en tres minutos caminando estarás en pleno centro de la ciudad. En el barrio vas a encontrar un ambiente tranquilo y residencial libre de ruidos molestos. La zona está rodeada de parques, ideal para pasear o hacer ejercicio al aire libre. También hay varios comercios y supermercados donde puedes hacer tus compras diarias. A poca distancia, puedes disfrutar de una variedad de restaurantes y cafeterías que ofrecen opciones locales e internacionales. Sin duda un lugar privilegiado para vivir en Segovia. Las condiciones para alquilar son: - 1 mes de fianza - 1 mes de depósito adicional - El mes en curso - Se solicitará al inquilino que contrate un Seguro de Responsabilidad Civil Disponemos de una amplia cartera de pisos con diferentes características para cubrir todas tus necesidades. ¡Consúltanos sin compromiso y únete a la revolución del alquiler Zazume!</t>
+        </is>
+      </c>
+      <c r="AT73" t="inlineStr">
+        <is>
+          <t>17/01/2026</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/110336547/</t>
+        </is>
+      </c>
+      <c r="AV73" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr"/>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Alquiler de piso en Centro</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>900</v>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>un día</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>1059</v>
+      </c>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="n">
+        <v>3</v>
+      </c>
+      <c r="L74" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>piso</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2ª</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr"/>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr"/>
+      <c r="AB74" t="inlineStr"/>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Distrito Centro</t>
+        </is>
+      </c>
+      <c r="AD74" t="inlineStr"/>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="AG74" t="inlineStr"/>
+      <c r="AH74" t="inlineStr"/>
+      <c r="AI74" t="inlineStr"/>
+      <c r="AJ74" t="inlineStr"/>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Segunda mano / buen estado</t>
+        </is>
+      </c>
+      <c r="AL74" t="inlineStr"/>
+      <c r="AM74" t="inlineStr"/>
+      <c r="AN74" t="inlineStr"/>
+      <c r="AO74" t="inlineStr"/>
+      <c r="AP74" t="inlineStr"/>
+      <c r="AQ74" t="inlineStr">
+        <is>
+          <t>Agencia</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>Inmosales</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr"/>
+      <c r="AT74" t="inlineStr">
+        <is>
+          <t>17/01/2026</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/110328709/</t>
+        </is>
+      </c>
+      <c r="AV74" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AW74" t="inlineStr"/>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Alquiler de piso en Calle Hermanos Barral</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>1600</v>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>11 días</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" s="2" t="n">
+        <v>2105</v>
+      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="n">
+        <v>3</v>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>piso</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>3ª</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr"/>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>Hermanos Barral</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr"/>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Distrito Centro</t>
+        </is>
+      </c>
+      <c r="AD75" t="inlineStr"/>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="AG75" t="inlineStr"/>
+      <c r="AH75" t="inlineStr"/>
+      <c r="AI75" t="inlineStr"/>
+      <c r="AJ75" t="inlineStr"/>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Segunda mano / buen estado</t>
+        </is>
+      </c>
+      <c r="AL75" t="inlineStr"/>
+      <c r="AM75" t="inlineStr"/>
+      <c r="AN75" t="inlineStr"/>
+      <c r="AO75" t="inlineStr"/>
+      <c r="AP75" t="inlineStr"/>
+      <c r="AQ75" t="inlineStr">
+        <is>
+          <t>Agencia</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>Leire de Bernedo</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr">
+        <is>
+          <t>TODO LOS GASTOS INCLUIDOS. ¡Descubre tu nuevo hogar en el corazón de la ciudad! Este espectacular piso en alquiler, situado en la tercera planta, ofrece unas vistas impresionantes que te dejarán sin aliento. Con 76 m² construidos, cuenta con 3 amplios dormitorios y 2 baños, ideal para compartir entre dos estudiantes. La luminosidad del espacio y su reciente reforma crean un ambiente acogedor y moderno. Ubicado a solo 5 minutos del emblemático acueducto y a 10 minutos de la plaza mayor, tendrás todo lo que necesitas a tu alcance. Además, la universidad está a menos de 15 minutos andando, lo que convierte a este piso en la opción perfecta para estudiantes que buscan comodidad y cercanía. El recibidor da paso a un salón espacioso y una cocina completamente equipada. Todos los gastos están incluidos, lo que te permitirá disfrutar de una vida sin preocupaciones. Servicio de limpieza includo. No pierdas la oportunidad de vivir en un lugar que combina ubicación, confort y estilo. ¡Ven a visitarlo y enamórate de tu nuevo hogar! *SOLO PARA ESTUDIANTES. *.</t>
+        </is>
+      </c>
+      <c r="AT75" t="inlineStr">
+        <is>
+          <t>17/01/2026</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/108078305/</t>
+        </is>
+      </c>
+      <c r="AV75" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AW75" t="inlineStr"/>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Alquiler de piso en Calle Larga, 4</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>8 días</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" s="2" t="n">
+        <v>1333</v>
+      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="n">
+        <v>4</v>
+      </c>
+      <c r="L76" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>piso</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>4ª</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr"/>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>Larga, 4</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr"/>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Distrito Centro</t>
+        </is>
+      </c>
+      <c r="AD76" t="inlineStr"/>
+      <c r="AE76" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="AG76" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AH76" t="inlineStr"/>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr"/>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Segunda mano / buen estado</t>
+        </is>
+      </c>
+      <c r="AL76" t="inlineStr"/>
+      <c r="AM76" t="inlineStr"/>
+      <c r="AN76" t="inlineStr"/>
+      <c r="AO76" t="inlineStr"/>
+      <c r="AP76" t="inlineStr"/>
+      <c r="AQ76" t="inlineStr">
+        <is>
+          <t>Agencia</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>BEYOND CAMPUS</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr"/>
+      <c r="AT76" t="inlineStr">
+        <is>
+          <t>17/01/2026</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/109765519/</t>
+        </is>
+      </c>
+      <c r="AV76" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AW76" t="inlineStr"/>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Alquiler de estudio en Calle Santa, 4</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>710</v>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>más de 2 meses</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" s="2" t="n">
+        <v>3737</v>
+      </c>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>estudio</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>estudio</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>3ª</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr"/>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>Santa, 4</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr"/>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Distrito Centro</t>
+        </is>
+      </c>
+      <c r="AD77" t="inlineStr"/>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AH77" t="inlineStr"/>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr"/>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Segunda mano / buen estado</t>
+        </is>
+      </c>
+      <c r="AL77" t="inlineStr"/>
+      <c r="AM77" t="inlineStr"/>
+      <c r="AN77" t="inlineStr"/>
+      <c r="AO77" t="inlineStr"/>
+      <c r="AP77" t="inlineStr"/>
+      <c r="AQ77" t="inlineStr">
+        <is>
+          <t>Agencia</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>BEYOND CAMPUS</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>Preferiblemente estudiantes de IE. Este acogedor estudio de 18 m² ofrece un espacio perfectamente distribuido que combina zona de descanso y salón en un ambiente práctico y bien aprovechado. El baño moderno aporta comodidad y funcionalidad, convirtiendo el estudio en una opción ideal para quienes buscan un hogar compacto pero bien equipado en una de las mejores zonas de Segovia. Situado a pocos minutos del emblemático Acueducto, el estudio disfruta de una ubicación excepcional dentro del casco histórico. La zona ofrece todo tipo de servicios: supermercados, cafeterías, restaurantes, tiendas y excelentes conexiones de transporte público, lo que facilita el día a día sin necesidad de largos desplazamientos. Su cercanía a IE University lo convierte en una alternativa especialmente atractiva para estudiantes que deseen vivir en un entorno cómodo, seguro y con todo a mano. El espacio ha sido diseñado para aprovechar al máximo la luz natural, creando un ambiente cálido y agradable durante todo el día. Su distribución eficiente permite disfrutar de un entorno práctico y confortable a pesar de su tamaño, siendo perfecto para quienes buscan independencia, tranquilidad y una ubicación privilegiada. En resumen, este estudio representa una oportunidad única para disfrutar de una vivienda funcional, luminosa y estratégicamente situada en pleno corazón de Segovia. Ideal para estudiantes de IE que buscan calidad de vida en un espacio pensado para su día a día.</t>
+        </is>
+      </c>
+      <c r="AT77" t="inlineStr">
+        <is>
+          <t>17/01/2026</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/109775479/</t>
+        </is>
+      </c>
+      <c r="AV77" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AW77" t="inlineStr"/>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -12122,7 +12614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AX7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12374,16 +12866,6 @@
       <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>Comunidad Autonoma</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>Lat</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>Lon</t>
         </is>
       </c>
     </row>
@@ -12554,12 +13036,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY2" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12718,12 +13194,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY3" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12880,12 +13350,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY4" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13044,12 +13508,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY5" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13218,11 +13676,165 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY6" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>-3.7038</v>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Alquiler de casa o chalet independiente en Calle de San Gabriel</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>1400</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Vía Roma</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>13 horas</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>1750</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>chalet</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>chalet</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>de San Gabriel</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Distrito Vía Roma</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Segunda mano / buen estado</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>Agencia</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>INNOVA HOUSE</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>ESTUDIANTES ie. APARTAMENTO CON GASTOS INCLUIDOS INNOVA HOUSE INMOBILIARIA, te ofrece este PRECIOSO PISO, situado en el centro de Segovia, próximo al acueducto y a 10 minutos andando a la IE University. CON TODOS LOS GASTOS INCLUIDOS EXCLUSIVO PARA ESTUDIANTES, ideal para estudiantes IE UNIVERSITY por su proximidad al campus. Recientemente reformado. Con mucha luz y claridad tiene una distribución muy cómoda para vivir. Distribuido en dos amplios dormitorios, 2 cuartos de baño completos con ducha, 1 aseo en planta baja. Cocina, salón y patio. El piso se alquila totalmente amueblado y equipado listo para vivir en él. Se entrega completamente amueblado y con T. V Precio para estudiantes con todos los gastos incluidos (luz, calefacción, agua caliente y fría, tasa de basura y WIFI) 1400€/mes WHATSAPP: INNOVA HOUSE INMOBILIARIA ALQUILA!</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>17/01/2026</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/108748247/</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -13236,7 +13848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AX3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13488,16 +14100,6 @@
       <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>Comunidad Autonoma</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>Lat</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>Lon</t>
         </is>
       </c>
     </row>
@@ -13672,12 +14274,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY2" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13843,12 +14439,6 @@
         <is>
           <t>Castilla y León</t>
         </is>
-      </c>
-      <c r="AY3" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>-3.7038</v>
       </c>
     </row>
   </sheetData>
@@ -13862,7 +14452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AX3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14114,16 +14704,6 @@
       <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>Comunidad Autonoma</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>Lat</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>Lon</t>
         </is>
       </c>
     </row>
@@ -14310,12 +14890,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY2" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14501,12 +15075,6 @@
         <is>
           <t>Castilla y León</t>
         </is>
-      </c>
-      <c r="AY3" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>-3.7038</v>
       </c>
     </row>
   </sheetData>
@@ -14520,7 +15088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AX5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14772,16 +15340,6 @@
       <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>Comunidad Autonoma</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>Lat</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>Lon</t>
         </is>
       </c>
     </row>
@@ -14948,12 +15506,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY2" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15100,12 +15652,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY3" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15258,12 +15804,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY4" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15423,12 +15963,6 @@
         <is>
           <t>Castilla y León</t>
         </is>
-      </c>
-      <c r="AY5" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>-3.7038</v>
       </c>
     </row>
   </sheetData>
@@ -15442,7 +15976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AX2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15694,16 +16228,6 @@
       <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>Comunidad Autonoma</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>Lat</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>Lon</t>
         </is>
       </c>
     </row>
@@ -15857,12 +16381,6 @@
         <is>
           <t>Castilla y León</t>
         </is>
-      </c>
-      <c r="AY2" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>-3.7038</v>
       </c>
     </row>
   </sheetData>
@@ -15876,7 +16394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16128,16 +16646,6 @@
       <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>Comunidad Autonoma</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>Lat</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>Lon</t>
         </is>
       </c>
     </row>
@@ -16294,8 +16802,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -16470,8 +16976,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -16646,8 +17150,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -16802,8 +17304,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16944,8 +17444,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16958,7 +17456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AX3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17210,16 +17708,6 @@
       <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>Comunidad Autonoma</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>Lat</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>Lon</t>
         </is>
       </c>
     </row>
@@ -17388,12 +17876,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY2" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17561,12 +18043,6 @@
         <is>
           <t>Castilla y León</t>
         </is>
-      </c>
-      <c r="AY3" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>-3.7038</v>
       </c>
     </row>
   </sheetData>
@@ -17580,7 +18056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AX2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17832,16 +18308,6 @@
       <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>Comunidad Autonoma</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>Lat</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>Lon</t>
         </is>
       </c>
     </row>
@@ -18011,12 +18477,6 @@
         <is>
           <t>Castilla y León</t>
         </is>
-      </c>
-      <c r="AY2" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>-3.7038</v>
       </c>
     </row>
   </sheetData>
@@ -18030,7 +18490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AX2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18282,16 +18742,6 @@
       <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>Comunidad Autonoma</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>Lat</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>Lon</t>
         </is>
       </c>
     </row>
@@ -18449,12 +18899,6 @@
         <is>
           <t>Castilla y León</t>
         </is>
-      </c>
-      <c r="AY2" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>-3.7038</v>
       </c>
     </row>
   </sheetData>
@@ -18468,7 +18912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AX3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18720,16 +19164,6 @@
       <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>Comunidad Autonoma</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>Lat</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>Lon</t>
         </is>
       </c>
     </row>
@@ -18906,12 +19340,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY2" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19063,12 +19491,6 @@
         <is>
           <t>Castilla y León</t>
         </is>
-      </c>
-      <c r="AY3" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>-3.7038</v>
       </c>
     </row>
   </sheetData>
@@ -19082,7 +19504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AX4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19334,16 +19756,6 @@
       <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>Comunidad Autonoma</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>Lat</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>Lon</t>
         </is>
       </c>
     </row>
@@ -19510,12 +19922,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY2" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19680,12 +20086,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY3" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19841,12 +20241,6 @@
         <is>
           <t>Castilla y León</t>
         </is>
-      </c>
-      <c r="AY4" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>-3.7038</v>
       </c>
     </row>
   </sheetData>
@@ -19860,7 +20254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AX15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20112,16 +20506,6 @@
       <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>Comunidad Autonoma</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>Lat</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>Lon</t>
         </is>
       </c>
     </row>
@@ -20274,12 +20658,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY2" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -20436,12 +20814,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY3" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -20592,12 +20964,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY4" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20758,12 +21124,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY5" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20918,12 +21278,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY6" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -21070,12 +21424,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY7" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21230,12 +21578,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY8" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21388,12 +21730,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY9" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21546,12 +21882,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY10" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -21708,12 +22038,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY11" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -21870,12 +22194,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY12" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -22022,12 +22340,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY13" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -22188,11 +22500,147 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY14" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>-3.7038</v>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Alquiler de piso en Paseo Conde de Sepúlveda</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>1350</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Ezequiel González - Cde. Sepulveda</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>14 horas</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" s="2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>piso</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1ª</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Distrito Ezequiel González - Cde. Sepulveda</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Segunda mano / buen estado</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>Agencia</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>VIZCAINOS HOME AWAY</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>17/01/2026</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/107876599/</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -22206,7 +22654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AX2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22458,16 +22906,6 @@
       <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>Comunidad Autonoma</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>Lat</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>Lon</t>
         </is>
       </c>
     </row>
@@ -22617,12 +23055,6 @@
         <is>
           <t>Castilla y León</t>
         </is>
-      </c>
-      <c r="AY2" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>-3.7038</v>
       </c>
     </row>
   </sheetData>
@@ -22636,7 +23068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ17"/>
+  <dimension ref="A1:AX20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22888,16 +23320,6 @@
       <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>Comunidad Autonoma</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>Lat</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>Lon</t>
         </is>
       </c>
     </row>
@@ -23050,12 +23472,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY2" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23222,12 +23638,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY3" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -23390,12 +23800,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY4" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23546,12 +23950,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY5" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23712,12 +24110,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY6" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -23882,12 +24274,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY7" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -24066,12 +24452,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY8" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24226,12 +24606,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY9" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24404,12 +24778,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY10" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24576,12 +24944,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY11" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -24748,12 +25110,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY12" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -24908,12 +25264,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY13" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -25074,12 +25424,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY14" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -25238,12 +25582,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY15" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -25394,12 +25732,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY16" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -25556,11 +25888,471 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY17" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>-3.7038</v>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Alquiler de piso en José Zorrilla - Padre Claret</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>875</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>16 horas</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" s="2" t="n">
+        <v>911</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="n">
+        <v>3</v>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>piso</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>3ª</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="n">
+        <v>1979</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Distrito José Zorrilla - Padre Claret</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Segunda mano / buen estado</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>Agencia</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>Paloma GMS</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>Ubicada junto al Campus María Zambrano de la Universidad de Valladolid, y a escasos metros de la Calle José Zorrilla, esta vivienda representa una oportunidad estratégica para quienes buscan residir en el centro neurálgico de Segovia, con todos los servicios, transporte y actividad universitaria a un paso. La vivienda se sitúa en una tercera planta sin ascensor y destaca por su excelente luminosidad y su carácter exterior al hacer chaflán completo del edificio. Distribución y características: - Hall de entrada y pasillo distribuidor. - Amplio salón-comedor en dos ambientes, totalmente amueblado, con: Chimenea. Bomba de aire frío/calor. Dos sofás, mueble de salón, pared de espejos y mesa de comedor. - Terraza acristalada perimetral, con gran entrada de luz natural y sensación de amplitud. - Carpintería interior de PVC con doble acristalamiento, ventanas oscilobatientes y contraventanas de aluminio. - Suelos de parquet en toda la vivienda. - Calefacción individualizada por contadores en cada radiador. - Cocina independiente, equipada a capricho: Todos los electrodomésticos. Hilo musical. Gran capacidad de almacenaje. Amplio ventanal y espacio para mesa de desayuno/comidas. Decoración en tonos amarillos y blancos que aporta un ambiente alegre y luminoso. - Tres dormitorios: Dormitorio principal con cama de matrimonio y armario empotrado de pared a pared. Dos dormitorios adicionales con camas encastradas en mobiliario a medida y zona de escritorio. -Persianas eléctricas en la vivienda. - Baño completo con bañera. - Condiciones del alquiler Se realizará Seguro de alquiler a cargo del propietario. 1 mes de fianza. 1 mes de garantía adicional. Mes en curso. Gastos suministros no incluidos. Una vivienda funcional, luminosa y perfectamente equipada, ideal para perfiles universitarios, profesionales o familias que valoren ubicación céntrica, amplitud y confort en una de las zonas más demandadas de Segovia. [IW].</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>17/01/2026</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/110326651/</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Alquiler de estudio en Calle Coronel Rexach, 8</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>790</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>José Zorrilla - Padre Claret</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>más de un mes</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" s="2" t="n">
+        <v>1317</v>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>estudio</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>1ª</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Coronel Rexach, 8</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Distrito José Zorrilla - Padre Claret</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Segunda mano / buen estado</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>Agencia</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>BEYOND CAMPUS</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>17/01/2026</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/110141435/</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr"/>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Alquiler de piso en Calle General Gutiérrez Mellado, 30</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>880</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>José Zorrilla - Padre Claret</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2 horas</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" s="2" t="n">
+        <v>1114</v>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>piso</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>orientación norte</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2ª</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>General Gutiérrez Mellado, 30</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Distrito José Zorrilla - Padre Claret</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Segunda mano / buen estado</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>Particular</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>Sergio Fresnillo</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>17/01/2026</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/101645182/</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr"/>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -25574,7 +26366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ123"/>
+  <dimension ref="A1:AX129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25826,16 +26618,6 @@
       <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>Comunidad Autonoma</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>Lat</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>Lon</t>
         </is>
       </c>
     </row>
@@ -25988,8 +26770,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -26124,12 +26904,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY3" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -26288,12 +27062,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY4" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -26454,12 +27222,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY5" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -26620,12 +27382,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY6" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -26788,12 +27544,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY7" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -26976,12 +27726,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY8" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -27140,12 +27884,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY9" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27320,12 +28058,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY10" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -27492,12 +28224,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY11" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -27644,12 +28370,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY12" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -27788,12 +28508,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY13" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -27932,12 +28646,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY14" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -28076,12 +28784,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY15" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -28220,12 +28922,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY16" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -28364,12 +29060,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY17" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -28512,12 +29202,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY18" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -28672,12 +29356,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY19" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -28820,12 +29498,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY20" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -28980,12 +29652,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY21" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -29148,12 +29814,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY22" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -29320,12 +29980,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY23" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -29480,12 +30134,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY24" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -29652,12 +30300,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY25" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -29808,12 +30450,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY26" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -29966,12 +30602,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY27" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -30110,12 +30740,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY28" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -30266,12 +30890,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY29" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -30432,12 +31050,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY30" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -30594,12 +31206,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY31" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -30758,12 +31364,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY32" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -30942,12 +31542,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY33" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -31086,12 +31680,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY34" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -31228,12 +31816,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY35" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -31388,12 +31970,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY36" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -31532,12 +32108,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY37" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -31684,12 +32254,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY38" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -31836,12 +32400,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY39" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -31988,12 +32546,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY40" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -32132,12 +32684,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY41" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ41" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -32288,12 +32834,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY42" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -32436,12 +32976,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY43" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ43" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -32590,12 +33124,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY44" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ44" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -32742,12 +33270,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY45" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ45" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -32886,12 +33408,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY46" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ46" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -33036,12 +33552,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY47" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ47" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -33184,12 +33694,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY48" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ48" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -33342,12 +33846,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY49" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ49" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -33486,12 +33984,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY50" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ50" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -33634,12 +34126,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY51" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ51" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -33782,12 +34268,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY52" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ52" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -33930,12 +34410,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY53" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ53" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -34080,12 +34554,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY54" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ54" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -34228,12 +34696,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY55" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ55" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -34386,12 +34848,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY56" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ56" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -34530,12 +34986,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY57" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ57" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -34694,12 +35144,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY58" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ58" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -34842,12 +35286,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY59" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ59" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -35026,12 +35464,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY60" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ60" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -35194,12 +35626,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY61" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ61" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -35346,12 +35772,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY62" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ62" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -35498,12 +35918,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY63" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ63" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -35678,12 +36092,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY64" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ64" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -35844,12 +36252,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY65" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ65" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -35996,12 +36398,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY66" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ66" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -36152,12 +36548,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY67" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ67" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -36310,12 +36700,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY68" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ68" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -36466,12 +36850,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY69" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ69" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -36634,12 +37012,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY70" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ70" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -36802,12 +37174,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY71" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ71" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -36966,12 +37332,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY72" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ72" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -37126,12 +37486,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY73" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ73" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -37294,12 +37648,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY74" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ74" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -37454,12 +37802,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY75" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ75" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -37638,12 +37980,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY76" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ76" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -37798,12 +38134,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY77" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ77" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -37942,12 +38272,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY78" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ78" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -38086,12 +38410,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY79" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ79" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -38234,12 +38552,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY80" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ80" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -38382,12 +38694,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY81" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ81" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -38536,12 +38842,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY82" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ82" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -38696,12 +38996,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY83" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ83" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -38852,12 +39146,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY84" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ84" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -39018,12 +39306,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY85" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ85" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -39188,12 +39470,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY86" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ86" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -39358,12 +39634,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY87" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ87" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -39500,12 +39770,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY88" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ88" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -39656,12 +39920,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY89" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ89" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -39804,12 +40062,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY90" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ90" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -39974,12 +40226,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY91" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ91" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -40140,12 +40386,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY92" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ92" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -40298,12 +40538,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY93" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ93" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -40484,12 +40718,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY94" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ94" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -40650,12 +40878,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY95" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ95" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -40816,12 +41038,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY96" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ96" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -40972,12 +41188,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY97" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ97" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -41132,12 +41342,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY98" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ98" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -41284,12 +41488,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY99" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ99" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -41440,12 +41638,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY100" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ100" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -41608,12 +41800,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY101" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ101" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -41760,12 +41946,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY102" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ102" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -41926,12 +42106,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY103" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ103" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -42078,12 +42252,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY104" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ104" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -42236,12 +42404,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY105" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ105" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -42386,12 +42548,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY106" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ106" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -42552,12 +42708,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY107" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ107" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -42708,12 +42858,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY108" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ108" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -42860,12 +43004,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY109" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ109" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -43008,12 +43146,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY110" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ110" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -43178,12 +43310,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY111" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ111" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -43336,12 +43462,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY112" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ112" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -43512,12 +43632,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY113" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ113" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -43668,12 +43782,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY114" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ114" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -43834,12 +43942,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY115" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ115" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -43988,12 +44090,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY116" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ116" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -44146,12 +44242,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY117" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ117" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -44320,12 +44410,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY118" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ118" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -44478,12 +44562,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY119" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ119" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -44634,12 +44712,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY120" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ120" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -44788,12 +44860,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY121" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ121" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -44936,12 +45002,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY122" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ122" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -45110,11 +45170,909 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY123" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ123" t="n">
-        <v>-3.7038</v>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Alquiler de piso en Calle Leopoldo Moreno</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="n">
+        <v>1300</v>
+      </c>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Plaza Mayor - San Agustín</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>un día</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>1083</v>
+      </c>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="n">
+        <v>4</v>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr"/>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>piso</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr"/>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr"/>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr"/>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>Leopoldo Moreno</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr"/>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Distrito Plaza Mayor - San Agustín</t>
+        </is>
+      </c>
+      <c r="AD124" t="inlineStr"/>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="AF124" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="AG124" t="inlineStr"/>
+      <c r="AH124" t="inlineStr"/>
+      <c r="AI124" t="inlineStr"/>
+      <c r="AJ124" t="inlineStr"/>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>Segunda mano / buen estado</t>
+        </is>
+      </c>
+      <c r="AL124" t="inlineStr"/>
+      <c r="AM124" t="inlineStr"/>
+      <c r="AN124" t="inlineStr"/>
+      <c r="AO124" t="inlineStr"/>
+      <c r="AP124" t="inlineStr"/>
+      <c r="AQ124" t="inlineStr">
+        <is>
+          <t>Agencia</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>Inmosales</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr"/>
+      <c r="AT124" t="inlineStr">
+        <is>
+          <t>17/01/2026</t>
+        </is>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/106420543/</t>
+        </is>
+      </c>
+      <c r="AV124" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AW124" t="inlineStr"/>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Alquiler de estudio en Calle de la Herrería, 10</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Plaza Mayor - San Agustín</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>más de un mes</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" s="2" t="n">
+        <v>2308</v>
+      </c>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="n">
+        <v>1</v>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr"/>
+      <c r="Q125" t="inlineStr"/>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>estudio</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr"/>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr"/>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr"/>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>de la Herrería, 10</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr"/>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Distrito Plaza Mayor - San Agustín</t>
+        </is>
+      </c>
+      <c r="AD125" t="inlineStr"/>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AH125" t="inlineStr"/>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr"/>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>Segunda mano / buen estado</t>
+        </is>
+      </c>
+      <c r="AL125" t="inlineStr"/>
+      <c r="AM125" t="inlineStr"/>
+      <c r="AN125" t="inlineStr"/>
+      <c r="AO125" t="inlineStr"/>
+      <c r="AP125" t="inlineStr"/>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>Agencia</t>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>BEYOND CAMPUS</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>Apartamento de 1 dormitorio totalmente amueblado junto a Plaza Mayor – solo para estudiantes de IE University Este luminoso y acogedor apartamento de un dormitorio se encuentra a solo unos pasos de la emblemática Plaza Mayor, en pleno centro de Segovia. Cuenta con un dormitorio con cama doble, un baño moderno, un salón confortable con sofá cama para invitados y una cocina totalmente equipada con electrodomésticos y menaje. Dispone de entrada privada e independiente, lo que garantiza comodidad e intimidad. Es ideal para estudiantes de IE University que buscan un lugar tranquilo y céntrico para vivir, con todos los servicios al alcance: supermercados, cafeterías, restaurantes y transporte público. Perfecto tanto para estudiar como para relajarse, este encantador y funcional apartamento ofrece el equilibrio ideal entre comodidad y tranquilidad en uno de los barrios más vivos y con más encanto de Segovia.</t>
+        </is>
+      </c>
+      <c r="AT125" t="inlineStr">
+        <is>
+          <t>17/01/2026</t>
+        </is>
+      </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/108732485/</t>
+        </is>
+      </c>
+      <c r="AV125" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AW125" t="inlineStr"/>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Alquiler de piso en Calle San Facundo</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Plaza Mayor - San Agustín</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>17 días</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" s="2" t="n">
+        <v>2100</v>
+      </c>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="n">
+        <v>3</v>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr"/>
+      <c r="Q126" t="inlineStr"/>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>piso</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr"/>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr"/>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>1ª</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr"/>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>San Facundo</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr"/>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Distrito Plaza Mayor - San Agustín</t>
+        </is>
+      </c>
+      <c r="AD126" t="inlineStr"/>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="AG126" t="inlineStr"/>
+      <c r="AH126" t="inlineStr"/>
+      <c r="AI126" t="inlineStr"/>
+      <c r="AJ126" t="inlineStr"/>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>Segunda mano / buen estado</t>
+        </is>
+      </c>
+      <c r="AL126" t="inlineStr"/>
+      <c r="AM126" t="inlineStr"/>
+      <c r="AN126" t="inlineStr"/>
+      <c r="AO126" t="inlineStr"/>
+      <c r="AP126" t="inlineStr"/>
+      <c r="AQ126" t="inlineStr">
+        <is>
+          <t>Agencia</t>
+        </is>
+      </c>
+      <c r="AR126" t="inlineStr"/>
+      <c r="AS126" t="inlineStr"/>
+      <c r="AT126" t="inlineStr">
+        <is>
+          <t>17/01/2026</t>
+        </is>
+      </c>
+      <c r="AU126" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/96633470/</t>
+        </is>
+      </c>
+      <c r="AV126" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AW126" t="inlineStr"/>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Alquiler de piso en Calle del Mal Consejo</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="n">
+        <v>1450</v>
+      </c>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Plaza Mayor - San Agustín</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>16 horas</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" s="2" t="n">
+        <v>1933</v>
+      </c>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="n">
+        <v>2</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
+      <c r="P127" t="inlineStr"/>
+      <c r="Q127" t="inlineStr"/>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>piso</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr"/>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr"/>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr"/>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>del Mal Consejo</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr"/>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Distrito Plaza Mayor - San Agustín</t>
+        </is>
+      </c>
+      <c r="AD127" t="inlineStr"/>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="AG127" t="inlineStr"/>
+      <c r="AH127" t="inlineStr"/>
+      <c r="AI127" t="inlineStr"/>
+      <c r="AJ127" t="inlineStr"/>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>Segunda mano / buen estado</t>
+        </is>
+      </c>
+      <c r="AL127" t="inlineStr"/>
+      <c r="AM127" t="inlineStr"/>
+      <c r="AN127" t="inlineStr"/>
+      <c r="AO127" t="inlineStr"/>
+      <c r="AP127" t="inlineStr"/>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>Agencia</t>
+        </is>
+      </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>VIZCAINOS HOME AWAY</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr"/>
+      <c r="AT127" t="inlineStr">
+        <is>
+          <t>17/01/2026</t>
+        </is>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/100929489/</t>
+        </is>
+      </c>
+      <c r="AV127" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AW127" t="inlineStr"/>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Alquiler de piso en juderia vieja</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="n">
+        <v>1300</v>
+      </c>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Plaza Mayor - San Agustín</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>16 horas</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" s="2" t="n">
+        <v>1529</v>
+      </c>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="n">
+        <v>2</v>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr"/>
+      <c r="P128" t="inlineStr"/>
+      <c r="Q128" t="inlineStr"/>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>piso</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr"/>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr"/>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>3ª</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr"/>
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr"/>
+      <c r="AB128" t="inlineStr"/>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Distrito Plaza Mayor - San Agustín</t>
+        </is>
+      </c>
+      <c r="AD128" t="inlineStr"/>
+      <c r="AE128" t="inlineStr">
+        <is>
+          <t>juderia vieja</t>
+        </is>
+      </c>
+      <c r="AF128" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="AG128" t="inlineStr"/>
+      <c r="AH128" t="inlineStr"/>
+      <c r="AI128" t="inlineStr"/>
+      <c r="AJ128" t="inlineStr"/>
+      <c r="AK128" t="inlineStr">
+        <is>
+          <t>Segunda mano / buen estado</t>
+        </is>
+      </c>
+      <c r="AL128" t="inlineStr"/>
+      <c r="AM128" t="inlineStr"/>
+      <c r="AN128" t="inlineStr"/>
+      <c r="AO128" t="inlineStr"/>
+      <c r="AP128" t="inlineStr"/>
+      <c r="AQ128" t="inlineStr">
+        <is>
+          <t>Agencia</t>
+        </is>
+      </c>
+      <c r="AR128" t="inlineStr">
+        <is>
+          <t>VIZCAINOS HOME AWAY</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr">
+        <is>
+          <t>Precioso apartamento super céntrico, muy luminoso y con salón a doble altura, ideal para estudiantes de IE University por su proximidad a la facultad. Dispone de dos habitaciones (una de ellas con balcón) y dos baños, completamente reformado, con 2 hermosos balcones que dan a la Calle Infanta Isabel (Calle Real), al lado de la Plaza Mayor y la Catedral. Con todo tipo de tiendas cerca, restaurantes y supermercados. En el corazón del casco histórico. Viene completamente amueblado y equipado. Además incluye en el precio el WiFi, limpieza semanal de 2 horas, gastos de comunidad, basuras y agua fría. El edificio dispone de ascensor. Complementariamente se puede contratar servicio de cambio de sábanas semanal. ¡ Exclusivo para nuestros clientes IE se incluye también la tarifa ONLY en nuestro Gimnasio VizcainosGYM! Contrato para 12 meses.</t>
+        </is>
+      </c>
+      <c r="AT128" t="inlineStr">
+        <is>
+          <t>17/01/2026</t>
+        </is>
+      </c>
+      <c r="AU128" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/103039865/</t>
+        </is>
+      </c>
+      <c r="AV128" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AW128" t="inlineStr"/>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Alquiler de ático en Calle la Judería Vieja</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="n">
+        <v>1300</v>
+      </c>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Plaza Mayor - San Agustín</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>16 horas</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" s="2" t="n">
+        <v>1625</v>
+      </c>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="n">
+        <v>2</v>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr"/>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>atico</t>
+        </is>
+      </c>
+      <c r="S129" t="inlineStr"/>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>orientación sur</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>3ª</t>
+        </is>
+      </c>
+      <c r="W129" s="2" t="n">
+        <v>2016</v>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>la Judería Vieja</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr"/>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Distrito Plaza Mayor - San Agustín</t>
+        </is>
+      </c>
+      <c r="AD129" t="inlineStr"/>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="AG129" t="inlineStr"/>
+      <c r="AH129" t="inlineStr"/>
+      <c r="AI129" t="inlineStr"/>
+      <c r="AJ129" t="inlineStr"/>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>Segunda mano / buen estado</t>
+        </is>
+      </c>
+      <c r="AL129" t="inlineStr"/>
+      <c r="AM129" t="inlineStr"/>
+      <c r="AN129" t="inlineStr"/>
+      <c r="AO129" t="inlineStr"/>
+      <c r="AP129" t="inlineStr"/>
+      <c r="AQ129" t="inlineStr">
+        <is>
+          <t>Agencia</t>
+        </is>
+      </c>
+      <c r="AR129" t="inlineStr">
+        <is>
+          <t>PEOPLE &amp; HOME PROYECTOS Y SERVICIOS INMOBILIARIOS</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr">
+        <is>
+          <t>Precioso apartamento super céntrico, muy luminoso y con salón a doble altura, ideal para estudiantes de IE University por su proximidad a la facultad. Dispone de dos habitaciones (una de ellas con balcón) y un baño, completamente reformado, con 2 hermosos balcones que dan a la Calle Infanta Isabel (Calle Real), al lado de la Plaza Mayor y la Catedral. Con todo tipo de tiendas cerca, restaurantes y supermercados. En el corazón del casco histórico. Viene completamente amueblado y equipado. Además incluye en el precio el WiFi, limpieza semanal de 2 horas, gastos de comunidad, basuras y agua fría. El edificio dispone de ascensor. Complementariamente se puede contratar servicio de cambio de sábanas semanal. ¡ Exclusivo para nuestros clientes IE se incluye también la tarifa ONLY en nuestro Gimnasio VizcainosGYM! Contrato para 12 meses.</t>
+        </is>
+      </c>
+      <c r="AT129" t="inlineStr">
+        <is>
+          <t>17/01/2026</t>
+        </is>
+      </c>
+      <c r="AU129" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/87427347/</t>
+        </is>
+      </c>
+      <c r="AV129" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AW129" t="inlineStr"/>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -45128,7 +46086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ16"/>
+  <dimension ref="A1:AX16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45380,16 +46338,6 @@
       <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>Comunidad Autonoma</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>Lat</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>Lon</t>
         </is>
       </c>
     </row>
@@ -45542,12 +46490,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY2" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -45716,12 +46658,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY3" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -45872,12 +46808,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY4" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -46026,12 +46956,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY5" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -46194,12 +47118,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY6" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -46374,12 +47292,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY7" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -46524,12 +47436,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY8" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -46680,12 +47586,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY9" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -46840,12 +47740,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY10" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -47016,12 +47910,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY11" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -47164,12 +48052,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY12" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -47336,12 +48218,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY13" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -47502,12 +48378,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY14" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -47664,12 +48534,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY15" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -47829,12 +48693,6 @@
         <is>
           <t>Castilla y León</t>
         </is>
-      </c>
-      <c r="AY16" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>-3.7038</v>
       </c>
     </row>
   </sheetData>
@@ -47848,7 +48706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AX9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48100,16 +48958,6 @@
       <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>Comunidad Autonoma</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>Lat</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>Lon</t>
         </is>
       </c>
     </row>
@@ -48274,12 +49122,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY2" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -48432,12 +49274,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY3" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -48590,12 +49426,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY4" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -48740,12 +49570,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY5" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -48910,12 +49734,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY6" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -49072,12 +49890,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY7" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -49230,12 +50042,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY8" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -49386,12 +50192,6 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="AY9" t="n">
-        <v>40.4168</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>-3.7038</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
